--- a/docs/测试用例/SynaRoute测试用例-4-Codex.xlsx
+++ b/docs/测试用例/SynaRoute测试用例-4-Codex.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'用例'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'用例'!$A$1:$J$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -207,6 +213,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,7 +598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>版本 0.1.8    用例 14 条（其中 P0 必测 6 条）</t>
+          <t>版本 0.1.9    用例 19 条（其中 P0 必测 10 条）</t>
         </is>
       </c>
     </row>
@@ -763,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1494,15 +1503,243 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="10" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>v0.1.9 本轮修复（真机测出，重点回归）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>X-15</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Codex 接入后不再要求登录（本轮 P0）</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Codex 已安装；**先记下当前 ~/.codex/auth.json 的 sha256**（用于后面核对还原）</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>SynaRoute 里对 codex 分类点「启动代理并写入工具配置」→ 打开 Codex → 正常提问</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Codex **不再提示需要登录**，能正常对话；SynaRoute 运行日志里 codex 分类应出现 route/request 事件（上一版的症状是一条都没有，说明请求根本没到代理）</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Codex 界面 + SynaRoute 运行日志里 codex 分类有无 route 事件</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>X-16</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>auth.json 被换成占位但可完整还原</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>承接 X-15（已接入）</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>查看 ~/.codex/auth.json → 应只有一个 OPENAI_API_KEY 占位；再查看 auth.json.synaroute.bak → 应是接入前的**真实内容**（ChatGPT 登录态含 tokens）</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>占位文件里**不能**同时存在 tokens 与 OPENAI_API_KEY（混合态会让桌面端判成 api-key 模式撞账号门）；.bak 必须是接入前真实快照</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>对比两个文件内容；.bak 的 sha256 应等于 X-15 记下的那个</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>X-17</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>还原后 ChatGPT 登录态回来</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>承接 X-16</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>SynaRoute 里点「还原」或停止代理 → 再打开 Codex</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>auth.json 恢复为接入前内容（sha256 与 X-15 记下的一致）；Codex 回到官方登录态、可直接使用；.bak 已被删除</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>sha256 比对 + Codex 实际可用性</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>X-18</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>重复接入不冲掉原始登录态备份</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>承接 X-17（已还原）</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>再次接入 → 改一下代理端口 → 再接入一次 → 查看 .bak</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>.bak 始终是**最初的**真实 auth.json，不会被「已接入态」覆盖（否则还原只能拿回一个占位，用户永久失去官方登录）</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>查看 .bak 内容与 sha256</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>X-19</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>拉取模型失败提示可行动</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>codex 分类里从 cc-switch 导入的 Key（如 nimabo / 君の公益）</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>点「拉取模型」</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>连不上的应说「连不上…请检查 Base URL / 域名 / 是否需要代理」；返回网页的应说「返回的是网页而不是 JSON」。**不得**再出现 expected value at line 1 column 1</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>错误提示原文</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J18"/>
-  <mergeCells count="3">
+  <autoFilter ref="A1:J24"/>
+  <mergeCells count="4">
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败,阻塞,跳过"</formula1>
     </dataValidation>
   </dataValidations>
